--- a/Capstone Team Plan.xlsx
+++ b/Capstone Team Plan.xlsx
@@ -709,7 +709,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>OPEN — not yet chosen. Needed before AI agents can be wired to a real model.</t>
+          <t>RESOLVED — Google Gemini. Model: gemini-flash-latest (Google-maintained alias, avoids hardcoding a version that goes stale). Key is live in Railway (GEMINI_API_KEY). Connectivity smoke-tested successfully (scripts/test_llm_connection.py).</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>YES — must decide this week</t>
+          <t>No — done</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>This is Claude's first-cut assignment based on the only real signal available (Rahul = group admin, Sweta has driven direction) — not a claim about anyone's actual skills. Swap names in under 2 minutes on the call; the roles and responsibilities themselves are the part that's actually decided.</t>
